--- a/Gerbers/V2/PickAndPlace_V2.xlsx
+++ b/Gerbers/V2/PickAndPlace_V2.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="PickAndPlace_PCB2_2026_08_02" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="PickAndPlace_PCB2_2026_09_16" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="157">
   <si>
     <t>Designator</t>
   </si>
@@ -304,48 +304,51 @@
     <t>C0402</t>
   </si>
   <si>
+    <t>20.193mm</t>
+  </si>
+  <si>
+    <t>-17.018mm</t>
+  </si>
+  <si>
+    <t>19.648mm</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>ZX-SH1.0-8PWT</t>
+  </si>
+  <si>
+    <t>CONN-SMD_8P-P1.00_MEGASTAR_ZX-SH1.0-8PWT</t>
+  </si>
+  <si>
+    <t>10.16mm</t>
+  </si>
+  <si>
+    <t>-15.621mm</t>
+  </si>
+  <si>
+    <t>11.86mm</t>
+  </si>
+  <si>
+    <t>-19.121mm</t>
+  </si>
+  <si>
+    <t>U4</t>
+  </si>
+  <si>
+    <t>DS3231MZ+</t>
+  </si>
+  <si>
+    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
+  </si>
+  <si>
     <t>19.05mm</t>
   </si>
   <si>
-    <t>-17.399mm</t>
-  </si>
-  <si>
-    <t>19.595mm</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>EXP</t>
-  </si>
-  <si>
-    <t>ZX-SH1.0-8PWT</t>
-  </si>
-  <si>
-    <t>CONN-SMD_8P-P1.00_MEGASTAR_ZX-SH1.0-8PWT</t>
-  </si>
-  <si>
-    <t>10.16mm</t>
-  </si>
-  <si>
-    <t>-15.621mm</t>
-  </si>
-  <si>
-    <t>11.86mm</t>
-  </si>
-  <si>
-    <t>-19.121mm</t>
-  </si>
-  <si>
-    <t>U4</t>
-  </si>
-  <si>
-    <t>DS3231MZ+</t>
-  </si>
-  <si>
-    <t>SOIC-8_L4.9-W3.9-P1.27-LS6.0-BL</t>
-  </si>
-  <si>
     <t>-11.176mm</t>
   </si>
   <si>
@@ -419,6 +422,66 @@
   </si>
   <si>
     <t>220Ω</t>
+  </si>
+  <si>
+    <t>3.3V</t>
+  </si>
+  <si>
+    <t>25.008mm</t>
+  </si>
+  <si>
+    <t>-5.359mm</t>
+  </si>
+  <si>
+    <t>EN</t>
+  </si>
+  <si>
+    <t>-8.298mm</t>
+  </si>
+  <si>
+    <t>FB1</t>
+  </si>
+  <si>
+    <t>CBM100505U201T</t>
+  </si>
+  <si>
+    <t>L0402</t>
+  </si>
+  <si>
+    <t>51.689mm</t>
+  </si>
+  <si>
+    <t>-37.846mm</t>
+  </si>
+  <si>
+    <t>-38.391mm</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>0402WGF2001TCE</t>
+  </si>
+  <si>
+    <t>R0402</t>
+  </si>
+  <si>
+    <t>16.891mm</t>
+  </si>
+  <si>
+    <t>-19.05mm</t>
+  </si>
+  <si>
+    <t>16.458mm</t>
+  </si>
+  <si>
+    <t>2kΩ</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>-17.78mm</t>
   </si>
 </sst>
 </file>
@@ -795,7 +858,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="15" width="20" customWidth="1"/>
@@ -1541,7 +1604,7 @@
         <v>22</v>
       </c>
       <c r="L16">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="M16" t="s">
         <v>23</v>
@@ -1611,22 +1674,22 @@
         <v>110</v>
       </c>
       <c r="D18" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="E18" t="s">
+        <v>112</v>
+      </c>
+      <c r="F18" t="s">
         <v>111</v>
       </c>
-      <c r="F18" t="s">
-        <v>97</v>
-      </c>
       <c r="G18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I18" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J18">
         <v>8</v>
@@ -1649,7 +1712,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" t="s">
         <v>83</v>
@@ -1658,22 +1721,22 @@
         <v>84</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E19" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" t="s">
         <v>116</v>
       </c>
-      <c r="F19" t="s">
-        <v>115</v>
-      </c>
       <c r="G19" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" t="s">
         <v>116</v>
       </c>
-      <c r="H19" t="s">
-        <v>115</v>
-      </c>
       <c r="I19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -1696,31 +1759,31 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
         <v>121</v>
       </c>
-      <c r="F20" t="s">
-        <v>120</v>
-      </c>
       <c r="G20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J20">
         <v>4</v>
@@ -1735,39 +1798,39 @@
         <v>23</v>
       </c>
       <c r="N20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O20" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F21" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H21" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I21" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J21">
         <v>4</v>
@@ -1782,39 +1845,39 @@
         <v>23</v>
       </c>
       <c r="N21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="O21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C22" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F22" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G22" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H22" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I22" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J22">
         <v>4</v>
@@ -1829,10 +1892,245 @@
         <v>23</v>
       </c>
       <c r="N22" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O22" t="s">
-        <v>135</v>
+        <v>136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>137</v>
+      </c>
+      <c r="B23" t="s">
+        <v>83</v>
+      </c>
+      <c r="C23" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" t="s">
+        <v>138</v>
+      </c>
+      <c r="E23" t="s">
+        <v>139</v>
+      </c>
+      <c r="F23" t="s">
+        <v>138</v>
+      </c>
+      <c r="G23" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I23" t="s">
+        <v>139</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23" t="s">
+        <v>22</v>
+      </c>
+      <c r="L23">
+        <v>180</v>
+      </c>
+      <c r="M23" t="s">
+        <v>23</v>
+      </c>
+      <c r="N23" t="s">
+        <v>83</v>
+      </c>
+      <c r="O23" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>140</v>
+      </c>
+      <c r="B24" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" t="s">
+        <v>138</v>
+      </c>
+      <c r="E24" t="s">
+        <v>141</v>
+      </c>
+      <c r="F24" t="s">
+        <v>138</v>
+      </c>
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" t="s">
+        <v>138</v>
+      </c>
+      <c r="I24" t="s">
+        <v>141</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24">
+        <v>180</v>
+      </c>
+      <c r="M24" t="s">
+        <v>23</v>
+      </c>
+      <c r="N24" t="s">
+        <v>83</v>
+      </c>
+      <c r="O24" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>145</v>
+      </c>
+      <c r="E25" t="s">
+        <v>146</v>
+      </c>
+      <c r="F25" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25" t="s">
+        <v>146</v>
+      </c>
+      <c r="H25" t="s">
+        <v>145</v>
+      </c>
+      <c r="I25" t="s">
+        <v>147</v>
+      </c>
+      <c r="J25">
+        <v>2</v>
+      </c>
+      <c r="K25" t="s">
+        <v>22</v>
+      </c>
+      <c r="L25">
+        <v>90</v>
+      </c>
+      <c r="M25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N25" t="s">
+        <v>143</v>
+      </c>
+      <c r="O25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" t="s">
+        <v>151</v>
+      </c>
+      <c r="E26" t="s">
+        <v>152</v>
+      </c>
+      <c r="F26" t="s">
+        <v>151</v>
+      </c>
+      <c r="G26" t="s">
+        <v>152</v>
+      </c>
+      <c r="H26" t="s">
+        <v>153</v>
+      </c>
+      <c r="I26" t="s">
+        <v>152</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
+        <v>22</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26" t="s">
+        <v>23</v>
+      </c>
+      <c r="N26" t="s">
+        <v>154</v>
+      </c>
+      <c r="O26" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>155</v>
+      </c>
+      <c r="B27" t="s">
+        <v>149</v>
+      </c>
+      <c r="C27" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" t="s">
+        <v>151</v>
+      </c>
+      <c r="E27" t="s">
+        <v>156</v>
+      </c>
+      <c r="F27" t="s">
+        <v>151</v>
+      </c>
+      <c r="G27" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" t="s">
+        <v>153</v>
+      </c>
+      <c r="I27" t="s">
+        <v>156</v>
+      </c>
+      <c r="J27">
+        <v>2</v>
+      </c>
+      <c r="K27" t="s">
+        <v>22</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27" t="s">
+        <v>23</v>
+      </c>
+      <c r="N27" t="s">
+        <v>154</v>
+      </c>
+      <c r="O27" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
